--- a/01_analyses_mask-cropland/results/SoIB_summaries.xlsx
+++ b/01_analyses_mask-cropland/results/SoIB_summaries.xlsx
@@ -396,13 +396,13 @@
         <v>5</v>
       </c>
       <c r="C2">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D2">
-        <v>41.7</v>
+        <v>38.5</v>
       </c>
       <c r="E2">
-        <v>9.1</v>
+        <v>9.699999999999999</v>
       </c>
     </row>
     <row r="3">
@@ -415,13 +415,13 @@
         <v>4</v>
       </c>
       <c r="C3">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="D3">
-        <v>33.3</v>
+        <v>30.8</v>
       </c>
       <c r="E3">
-        <v>40.9</v>
+        <v>35.5</v>
       </c>
     </row>
     <row r="4">
@@ -431,16 +431,16 @@
         </is>
       </c>
       <c r="B4">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C4">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="D4">
-        <v>16.7</v>
+        <v>23.1</v>
       </c>
       <c r="E4">
-        <v>40.9</v>
+        <v>41.9</v>
       </c>
     </row>
     <row r="5">
@@ -459,7 +459,7 @@
         <v>0</v>
       </c>
       <c r="E5">
-        <v>4.5</v>
+        <v>3.2</v>
       </c>
     </row>
     <row r="6">
@@ -472,13 +472,13 @@
         <v>1</v>
       </c>
       <c r="C6">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D6">
-        <v>8.300000000000001</v>
+        <v>7.7</v>
       </c>
       <c r="E6">
-        <v>4.5</v>
+        <v>9.699999999999999</v>
       </c>
     </row>
     <row r="7">
@@ -488,10 +488,10 @@
         </is>
       </c>
       <c r="B7">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="C7">
-        <v>35</v>
+        <v>26</v>
       </c>
     </row>
     <row r="8">
@@ -643,7 +643,7 @@
         </is>
       </c>
       <c r="B4">
-        <v>554</v>
+        <v>553</v>
       </c>
     </row>
   </sheetData>
@@ -693,7 +693,7 @@
         <v>31</v>
       </c>
       <c r="C3">
-        <v>12</v>
+        <v>13</v>
       </c>
     </row>
     <row r="4">
@@ -706,7 +706,7 @@
         <v>57</v>
       </c>
       <c r="C4">
-        <v>22</v>
+        <v>31</v>
       </c>
     </row>
     <row r="5">

--- a/01_analyses_mask-cropland/results/SoIB_summaries.xlsx
+++ b/01_analyses_mask-cropland/results/SoIB_summaries.xlsx
@@ -399,10 +399,10 @@
         <v>3</v>
       </c>
       <c r="D2">
-        <v>33.3</v>
+        <v>38.5</v>
       </c>
       <c r="E2">
-        <v>10.7</v>
+        <v>9.699999999999999</v>
       </c>
     </row>
     <row r="3">
@@ -412,16 +412,16 @@
         </is>
       </c>
       <c r="B3">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="C3">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="D3">
-        <v>40</v>
+        <v>30.8</v>
       </c>
       <c r="E3">
-        <v>35.7</v>
+        <v>35.5</v>
       </c>
     </row>
     <row r="4">
@@ -434,13 +434,13 @@
         <v>3</v>
       </c>
       <c r="C4">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="D4">
-        <v>20</v>
+        <v>23.1</v>
       </c>
       <c r="E4">
-        <v>39.3</v>
+        <v>41.9</v>
       </c>
     </row>
     <row r="5">
@@ -453,13 +453,13 @@
         <v>0</v>
       </c>
       <c r="C5">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D5">
         <v>0</v>
       </c>
       <c r="E5">
-        <v>10.7</v>
+        <v>3.2</v>
       </c>
     </row>
     <row r="6">
@@ -472,13 +472,13 @@
         <v>1</v>
       </c>
       <c r="C6">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D6">
-        <v>6.7</v>
+        <v>7.7</v>
       </c>
       <c r="E6">
-        <v>3.6</v>
+        <v>9.699999999999999</v>
       </c>
     </row>
     <row r="7">
@@ -488,10 +488,10 @@
         </is>
       </c>
       <c r="B7">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="C7">
-        <v>29</v>
+        <v>26</v>
       </c>
     </row>
     <row r="8">
@@ -643,7 +643,7 @@
         </is>
       </c>
       <c r="B4">
-        <v>554</v>
+        <v>553</v>
       </c>
     </row>
   </sheetData>
@@ -693,7 +693,7 @@
         <v>31</v>
       </c>
       <c r="C3">
-        <v>15</v>
+        <v>13</v>
       </c>
     </row>
     <row r="4">
@@ -706,7 +706,7 @@
         <v>57</v>
       </c>
       <c r="C4">
-        <v>28</v>
+        <v>31</v>
       </c>
     </row>
     <row r="5">

--- a/01_analyses_mask-cropland/results/SoIB_summaries.xlsx
+++ b/01_analyses_mask-cropland/results/SoIB_summaries.xlsx
@@ -393,16 +393,16 @@
         </is>
       </c>
       <c r="B2">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="C2">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D2">
         <v>38.5</v>
       </c>
       <c r="E2">
-        <v>9.699999999999999</v>
+        <v>5</v>
       </c>
     </row>
     <row r="3">
@@ -412,16 +412,16 @@
         </is>
       </c>
       <c r="B3">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="C3">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="D3">
         <v>30.8</v>
       </c>
       <c r="E3">
-        <v>35.5</v>
+        <v>40</v>
       </c>
     </row>
     <row r="4">
@@ -431,16 +431,16 @@
         </is>
       </c>
       <c r="B4">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="C4">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="D4">
         <v>23.1</v>
       </c>
       <c r="E4">
-        <v>41.9</v>
+        <v>55</v>
       </c>
     </row>
     <row r="5">
@@ -450,16 +450,16 @@
         </is>
       </c>
       <c r="B5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D5">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="E5">
-        <v>3.2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="6">
@@ -472,13 +472,13 @@
         <v>1</v>
       </c>
       <c r="C6">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="D6">
-        <v>7.7</v>
+        <v>3.8</v>
       </c>
       <c r="E6">
-        <v>9.699999999999999</v>
+        <v>0</v>
       </c>
     </row>
     <row r="7">
@@ -488,10 +488,10 @@
         </is>
       </c>
       <c r="B7">
-        <v>18</v>
+        <v>5</v>
       </c>
       <c r="C7">
-        <v>26</v>
+        <v>37</v>
       </c>
     </row>
     <row r="8">
@@ -501,10 +501,10 @@
         </is>
       </c>
       <c r="B8">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="C8">
-        <v>41</v>
+        <v>40</v>
       </c>
     </row>
   </sheetData>
@@ -633,7 +633,7 @@
         </is>
       </c>
       <c r="B3">
-        <v>286</v>
+        <v>387</v>
       </c>
     </row>
     <row r="4">
@@ -643,7 +643,7 @@
         </is>
       </c>
       <c r="B4">
-        <v>553</v>
+        <v>441</v>
       </c>
     </row>
   </sheetData>
@@ -680,7 +680,7 @@
         </is>
       </c>
       <c r="B2">
-        <v>98</v>
+        <v>97</v>
       </c>
     </row>
     <row r="3">
@@ -693,7 +693,7 @@
         <v>31</v>
       </c>
       <c r="C3">
-        <v>13</v>
+        <v>26</v>
       </c>
     </row>
     <row r="4">
@@ -706,7 +706,7 @@
         <v>57</v>
       </c>
       <c r="C4">
-        <v>31</v>
+        <v>20</v>
       </c>
     </row>
     <row r="5">
@@ -772,7 +772,7 @@
         <v>88</v>
       </c>
       <c r="E2">
-        <v>98.90000000000001</v>
+        <v>95.7</v>
       </c>
     </row>
     <row r="3">
@@ -782,10 +782,10 @@
         </is>
       </c>
       <c r="B3">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C3">
-        <v>3.9</v>
+        <v>2.9</v>
       </c>
     </row>
     <row r="4">
@@ -795,16 +795,16 @@
         </is>
       </c>
       <c r="B4">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="C4">
-        <v>10.7</v>
+        <v>11.7</v>
       </c>
       <c r="D4">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="E4">
-        <v>1.1</v>
+        <v>4.3</v>
       </c>
     </row>
   </sheetData>
